--- a/input_template.xlsx
+++ b/input_template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Reli_DSM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\6-PDWM 2026\Jurnal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ABC9F27-B4B7-4865-9FA5-82A9BD72DB44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDEE72B3-74D2-47B5-B559-82F3F09F0D33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="797" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="797" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nodes" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="58">
   <si>
     <t>Node_ID</t>
   </si>
@@ -238,7 +238,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -299,6 +299,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -327,7 +339,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -349,15 +361,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -388,6 +391,36 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -692,7 +725,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -711,91 +744,102 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A2" s="2">
+      <c r="A2" s="3">
         <v>1</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="3">
         <v>0</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A3" s="2">
+      <c r="A3" s="3">
         <v>2</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="3">
+        <v>6000</v>
+      </c>
+      <c r="C3" s="3">
         <v>0</v>
       </c>
-      <c r="C3" s="2">
-        <v>3500</v>
-      </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A4" s="2">
+      <c r="A4" s="3">
         <v>3</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="3">
+        <v>11000</v>
+      </c>
+      <c r="C4" s="3">
         <v>0</v>
       </c>
-      <c r="C4" s="2">
-        <v>7000</v>
-      </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A5" s="2">
+      <c r="A5" s="3">
         <v>4</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="3">
         <v>0</v>
       </c>
-      <c r="C5" s="2">
-        <v>10500</v>
+      <c r="C5" s="3">
+        <v>4000</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A6" s="2">
+      <c r="A6" s="3">
         <v>5</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="3">
         <v>6000</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="3">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A7" s="3">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3">
+        <v>11000</v>
+      </c>
+      <c r="C7" s="3">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A8" s="3">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A7" s="2">
-        <v>6</v>
-      </c>
-      <c r="B7" s="2">
+      <c r="C8" s="3">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A9" s="3">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3">
         <v>6000</v>
       </c>
-      <c r="C7" s="2">
-        <v>3500</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A8" s="2">
-        <v>7</v>
-      </c>
-      <c r="B8" s="2">
-        <v>6000</v>
-      </c>
-      <c r="C8" s="2">
-        <v>7000</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A9" s="2">
-        <v>8</v>
-      </c>
-      <c r="B9" s="2">
-        <v>6000</v>
-      </c>
-      <c r="C9" s="2">
-        <v>10500</v>
+      <c r="C9" s="3">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A10" s="3">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3">
+        <v>11000</v>
+      </c>
+      <c r="C10" s="3">
+        <v>8000</v>
       </c>
     </row>
   </sheetData>
@@ -805,7 +849,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -813,8 +857,6 @@
     <col min="3" max="6" width="12" customWidth="1"/>
     <col min="7" max="9" width="15" customWidth="1"/>
     <col min="10" max="10" width="17" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.19921875" customWidth="1"/>
-    <col min="12" max="12" width="9.73046875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.45">
@@ -856,17 +898,17 @@
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A2" s="2">
+      <c r="A2" s="3">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="3">
         <v>1</v>
       </c>
-      <c r="D2" s="2">
-        <v>2</v>
+      <c r="D2" s="3">
+        <v>4</v>
       </c>
       <c r="E2" s="2">
         <v>300</v>
@@ -875,7 +917,7 @@
         <v>300</v>
       </c>
       <c r="G2" s="2">
-        <f t="shared" ref="G2:G10" si="0">E2*F2</f>
+        <f>E2*F2</f>
         <v>90000</v>
       </c>
       <c r="H2" s="7">
@@ -884,11 +926,11 @@
       </c>
       <c r="I2" s="2">
         <f>4700*SQRT(Mutu_Beton!$B$2)</f>
-        <v>26483.155023523912</v>
+        <v>20204.534144592399</v>
       </c>
       <c r="J2" s="2">
         <f>4700*SQRT(Mutu_Beton!$E$2)</f>
-        <v>23500</v>
+        <v>17928.624892924196</v>
       </c>
       <c r="K2" s="2">
         <v>0.7</v>
@@ -898,17 +940,17 @@
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A3" s="2">
+      <c r="A3" s="3">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="3">
         <v>2</v>
       </c>
-      <c r="D3" s="2">
-        <v>3</v>
+      <c r="D3" s="3">
+        <v>5</v>
       </c>
       <c r="E3" s="2">
         <v>300</v>
@@ -917,20 +959,20 @@
         <v>300</v>
       </c>
       <c r="G3" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="G3:G7" si="0">E3*F3</f>
         <v>90000</v>
       </c>
       <c r="H3" s="7">
-        <f t="shared" ref="H3:H10" si="1">(1/12)*E3*F3^3</f>
+        <f t="shared" ref="H3:H7" si="1">(1/12)*E3*F3^3</f>
         <v>675000000</v>
       </c>
       <c r="I3" s="2">
         <f>4700*SQRT(Mutu_Beton!$B$2)</f>
-        <v>26483.155023523912</v>
+        <v>20204.534144592399</v>
       </c>
       <c r="J3" s="2">
         <f>4700*SQRT(Mutu_Beton!$E$2)</f>
-        <v>23500</v>
+        <v>17928.624892924196</v>
       </c>
       <c r="K3" s="2">
         <v>0.7</v>
@@ -940,17 +982,17 @@
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A4" s="2">
+      <c r="A4" s="3">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="3">
         <v>3</v>
       </c>
-      <c r="D4" s="2">
-        <v>4</v>
+      <c r="D4" s="3">
+        <v>6</v>
       </c>
       <c r="E4" s="2">
         <v>300</v>
@@ -968,11 +1010,11 @@
       </c>
       <c r="I4" s="2">
         <f>4700*SQRT(Mutu_Beton!$B$2)</f>
-        <v>26483.155023523912</v>
+        <v>20204.534144592399</v>
       </c>
       <c r="J4" s="2">
         <f>4700*SQRT(Mutu_Beton!$E$2)</f>
-        <v>23500</v>
+        <v>17928.624892924196</v>
       </c>
       <c r="K4" s="2">
         <v>0.7</v>
@@ -982,17 +1024,17 @@
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A5" s="2">
+      <c r="A5" s="3">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C5" s="2">
-        <v>5</v>
-      </c>
-      <c r="D5" s="2">
-        <v>6</v>
+      <c r="C5" s="3">
+        <v>4</v>
+      </c>
+      <c r="D5" s="3">
+        <v>7</v>
       </c>
       <c r="E5" s="2">
         <v>300</v>
@@ -1010,11 +1052,11 @@
       </c>
       <c r="I5" s="2">
         <f>4700*SQRT(Mutu_Beton!$B$2)</f>
-        <v>26483.155023523912</v>
+        <v>20204.534144592399</v>
       </c>
       <c r="J5" s="2">
         <f>4700*SQRT(Mutu_Beton!$E$2)</f>
-        <v>23500</v>
+        <v>17928.624892924196</v>
       </c>
       <c r="K5" s="2">
         <v>0.7</v>
@@ -1024,17 +1066,17 @@
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A6" s="2">
+      <c r="A6" s="3">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C6" s="2">
-        <v>6</v>
-      </c>
-      <c r="D6" s="2">
-        <v>7</v>
+      <c r="C6" s="3">
+        <v>5</v>
+      </c>
+      <c r="D6" s="3">
+        <v>8</v>
       </c>
       <c r="E6" s="2">
         <v>300</v>
@@ -1052,11 +1094,11 @@
       </c>
       <c r="I6" s="2">
         <f>4700*SQRT(Mutu_Beton!$B$2)</f>
-        <v>26483.155023523912</v>
+        <v>20204.534144592399</v>
       </c>
       <c r="J6" s="2">
         <f>4700*SQRT(Mutu_Beton!$E$2)</f>
-        <v>23500</v>
+        <v>17928.624892924196</v>
       </c>
       <c r="K6" s="2">
         <v>0.7</v>
@@ -1066,17 +1108,17 @@
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A7" s="2">
+      <c r="A7" s="3">
         <v>6</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C7" s="2">
-        <v>7</v>
-      </c>
-      <c r="D7" s="2">
-        <v>8</v>
+      <c r="C7" s="3">
+        <v>6</v>
+      </c>
+      <c r="D7" s="3">
+        <v>9</v>
       </c>
       <c r="E7" s="2">
         <v>300</v>
@@ -1094,11 +1136,11 @@
       </c>
       <c r="I7" s="2">
         <f>4700*SQRT(Mutu_Beton!$B$2)</f>
-        <v>26483.155023523912</v>
+        <v>20204.534144592399</v>
       </c>
       <c r="J7" s="2">
         <f>4700*SQRT(Mutu_Beton!$E$2)</f>
-        <v>23500</v>
+        <v>17928.624892924196</v>
       </c>
       <c r="K7" s="2">
         <v>0.7</v>
@@ -1108,128 +1150,170 @@
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A8" s="2">
+      <c r="A8" s="25">
         <v>7</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="C8" s="2">
-        <v>2</v>
-      </c>
-      <c r="D8" s="2">
+      <c r="C8" s="25">
+        <v>4</v>
+      </c>
+      <c r="D8" s="25">
+        <v>5</v>
+      </c>
+      <c r="E8" s="26">
+        <v>300</v>
+      </c>
+      <c r="F8" s="26">
+        <v>500</v>
+      </c>
+      <c r="G8" s="26">
+        <f>E8*F8</f>
+        <v>150000</v>
+      </c>
+      <c r="H8" s="27">
+        <f>(1/12)*E8*F8^3</f>
+        <v>3125000000</v>
+      </c>
+      <c r="I8" s="26">
+        <f>4700*SQRT(Mutu_Beton!$B$2)</f>
+        <v>20204.534144592399</v>
+      </c>
+      <c r="J8" s="26">
+        <f>4700*SQRT(Mutu_Beton!$E$2)</f>
+        <v>17928.624892924196</v>
+      </c>
+      <c r="K8" s="26">
+        <v>0.7</v>
+      </c>
+      <c r="L8" s="26">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A9" s="25">
+        <v>8</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="C9" s="25">
+        <v>5</v>
+      </c>
+      <c r="D9" s="25">
         <v>6</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E9" s="26">
         <v>300</v>
       </c>
-      <c r="F8" s="2">
+      <c r="F9" s="26">
         <v>500</v>
       </c>
-      <c r="G8" s="2">
-        <f t="shared" si="0"/>
+      <c r="G9" s="26">
+        <f>E9*F9</f>
         <v>150000</v>
       </c>
-      <c r="H8" s="7">
-        <f t="shared" si="1"/>
+      <c r="H9" s="27">
+        <f>(1/12)*E9*F9^3</f>
         <v>3125000000</v>
       </c>
-      <c r="I8" s="2">
+      <c r="I9" s="26">
         <f>4700*SQRT(Mutu_Beton!$B$2)</f>
-        <v>26483.155023523912</v>
-      </c>
-      <c r="J8" s="2">
+        <v>20204.534144592399</v>
+      </c>
+      <c r="J9" s="26">
         <f>4700*SQRT(Mutu_Beton!$E$2)</f>
-        <v>23500</v>
-      </c>
-      <c r="K8" s="2">
+        <v>17928.624892924196</v>
+      </c>
+      <c r="K9" s="26">
         <v>0.7</v>
       </c>
-      <c r="L8" s="2">
+      <c r="L9" s="26">
         <v>0.2</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A9" s="2">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A10" s="20">
+        <v>9</v>
+      </c>
+      <c r="B10" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10" s="20">
+        <v>7</v>
+      </c>
+      <c r="D10" s="20">
         <v>8</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="E10" s="23">
+        <v>250</v>
+      </c>
+      <c r="F10" s="23">
+        <v>350</v>
+      </c>
+      <c r="G10" s="23">
+        <f t="shared" ref="G10:G11" si="2">E10*F10</f>
+        <v>87500</v>
+      </c>
+      <c r="H10" s="24">
+        <f>(1/12)*E10*F10^3</f>
+        <v>893229166.66666663</v>
+      </c>
+      <c r="I10" s="23">
+        <f>4700*SQRT(Mutu_Beton!$B$2)</f>
+        <v>20204.534144592399</v>
+      </c>
+      <c r="J10" s="23">
+        <f>4700*SQRT(Mutu_Beton!$E$2)</f>
+        <v>17928.624892924196</v>
+      </c>
+      <c r="K10" s="23">
+        <v>0.7</v>
+      </c>
+      <c r="L10" s="23">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A11" s="20">
+        <v>10</v>
+      </c>
+      <c r="B11" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="C9" s="2">
-        <v>3</v>
-      </c>
-      <c r="D9" s="2">
-        <v>7</v>
-      </c>
-      <c r="E9" s="2">
-        <v>300</v>
-      </c>
-      <c r="F9" s="2">
-        <v>500</v>
-      </c>
-      <c r="G9" s="2">
-        <f t="shared" si="0"/>
-        <v>150000</v>
-      </c>
-      <c r="H9" s="7">
-        <f t="shared" si="1"/>
-        <v>3125000000</v>
-      </c>
-      <c r="I9" s="2">
+      <c r="C11" s="20">
+        <v>8</v>
+      </c>
+      <c r="D11" s="20">
+        <v>9</v>
+      </c>
+      <c r="E11" s="23">
+        <v>250</v>
+      </c>
+      <c r="F11" s="23">
+        <v>350</v>
+      </c>
+      <c r="G11" s="23">
+        <f t="shared" si="2"/>
+        <v>87500</v>
+      </c>
+      <c r="H11" s="24">
+        <f>(1/12)*E11*F11^3</f>
+        <v>893229166.66666663</v>
+      </c>
+      <c r="I11" s="23">
         <f>4700*SQRT(Mutu_Beton!$B$2)</f>
-        <v>26483.155023523912</v>
-      </c>
-      <c r="J9" s="2">
+        <v>20204.534144592399</v>
+      </c>
+      <c r="J11" s="23">
         <f>4700*SQRT(Mutu_Beton!$E$2)</f>
-        <v>23500</v>
-      </c>
-      <c r="K9" s="2">
+        <v>17928.624892924196</v>
+      </c>
+      <c r="K11" s="23">
         <v>0.7</v>
       </c>
-      <c r="L9" s="2">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A10" s="2">
-        <v>9</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C10" s="2">
-        <v>4</v>
-      </c>
-      <c r="D10" s="2">
-        <v>8</v>
-      </c>
-      <c r="E10" s="4">
-        <v>200</v>
-      </c>
-      <c r="F10" s="4">
-        <v>300</v>
-      </c>
-      <c r="G10" s="2">
-        <f t="shared" si="0"/>
-        <v>60000</v>
-      </c>
-      <c r="H10" s="7">
-        <f t="shared" si="1"/>
-        <v>449999999.99999994</v>
-      </c>
-      <c r="I10" s="2">
-        <f>4700*SQRT(Mutu_Beton!$B$2)</f>
-        <v>26483.155023523912</v>
-      </c>
-      <c r="J10" s="2">
-        <f>4700*SQRT(Mutu_Beton!$E$2)</f>
-        <v>23500</v>
-      </c>
-      <c r="K10" s="2">
-        <v>0.7</v>
-      </c>
-      <c r="L10" s="2">
+      <c r="L11" s="23">
         <v>0.2</v>
       </c>
     </row>
@@ -1240,7 +1324,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1277,7 +1361,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A3" s="4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B3" s="4">
         <v>1</v>
@@ -1286,6 +1370,20 @@
         <v>1</v>
       </c>
       <c r="D3" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A4" s="4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4">
+        <v>1</v>
+      </c>
+      <c r="C4" s="4">
+        <v>1</v>
+      </c>
+      <c r="D4" s="4">
         <v>1</v>
       </c>
     </row>
@@ -1296,7 +1394,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1326,18 +1424,17 @@
         <v>1</v>
       </c>
       <c r="B2" s="3">
-        <f>1.27*E2</f>
-        <v>31.75</v>
+        <v>18.48</v>
       </c>
       <c r="C2" s="8">
-        <f>B2*10%</f>
-        <v>3.1750000000000003</v>
+        <v>3.32</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E2" s="8">
-        <v>25</v>
+        <f>B2/1.27</f>
+        <v>14.551181102362206</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.45">
@@ -1345,18 +1442,17 @@
         <v>2</v>
       </c>
       <c r="B3" s="3">
-        <f t="shared" ref="B3:B10" si="0">1.27*E3</f>
-        <v>31.75</v>
+        <v>18.48</v>
       </c>
       <c r="C3" s="8">
-        <f t="shared" ref="C3:C10" si="1">B3*10%</f>
-        <v>3.1750000000000003</v>
+        <v>3.32</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E3" s="8">
-        <v>25</v>
+        <f t="shared" ref="E3:E13" si="0">B3/1.27</f>
+        <v>14.551181102362206</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.45">
@@ -1364,18 +1460,17 @@
         <v>3</v>
       </c>
       <c r="B4" s="3">
-        <f t="shared" si="0"/>
-        <v>31.75</v>
+        <v>18.48</v>
       </c>
       <c r="C4" s="8">
-        <f t="shared" si="1"/>
-        <v>3.1750000000000003</v>
+        <v>3.32</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E4" s="8">
-        <v>25</v>
+        <f t="shared" si="0"/>
+        <v>14.551181102362206</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.45">
@@ -1383,18 +1478,17 @@
         <v>4</v>
       </c>
       <c r="B5" s="3">
-        <f t="shared" si="0"/>
-        <v>31.75</v>
+        <v>18.48</v>
       </c>
       <c r="C5" s="8">
-        <f t="shared" si="1"/>
-        <v>3.1750000000000003</v>
+        <v>3.32</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E5" s="8">
-        <v>25</v>
+        <f t="shared" si="0"/>
+        <v>14.551181102362206</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.45">
@@ -1402,18 +1496,17 @@
         <v>5</v>
       </c>
       <c r="B6" s="3">
-        <f t="shared" si="0"/>
-        <v>31.75</v>
+        <v>18.48</v>
       </c>
       <c r="C6" s="8">
-        <f t="shared" si="1"/>
-        <v>3.1750000000000003</v>
+        <v>3.32</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E6" s="8">
-        <v>25</v>
+        <f t="shared" si="0"/>
+        <v>14.551181102362206</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.45">
@@ -1421,18 +1514,17 @@
         <v>6</v>
       </c>
       <c r="B7" s="3">
-        <f t="shared" si="0"/>
-        <v>31.75</v>
+        <v>18.48</v>
       </c>
       <c r="C7" s="8">
-        <f t="shared" si="1"/>
-        <v>3.1750000000000003</v>
+        <v>3.32</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E7" s="8">
-        <v>25</v>
+        <f t="shared" si="0"/>
+        <v>14.551181102362206</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.45">
@@ -1440,18 +1532,17 @@
         <v>7</v>
       </c>
       <c r="B8" s="3">
-        <f t="shared" si="0"/>
-        <v>31.75</v>
+        <v>18.48</v>
       </c>
       <c r="C8" s="8">
-        <f t="shared" si="1"/>
-        <v>3.1750000000000003</v>
+        <v>3.32</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E8" s="8">
-        <v>25</v>
+        <f t="shared" si="0"/>
+        <v>14.551181102362206</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.45">
@@ -1459,18 +1550,17 @@
         <v>8</v>
       </c>
       <c r="B9" s="3">
-        <f t="shared" si="0"/>
-        <v>31.75</v>
+        <v>18.48</v>
       </c>
       <c r="C9" s="8">
-        <f t="shared" si="1"/>
-        <v>3.1750000000000003</v>
+        <v>3.32</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E9" s="8">
-        <v>25</v>
+        <f t="shared" si="0"/>
+        <v>14.551181102362206</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.45">
@@ -1478,18 +1568,71 @@
         <v>9</v>
       </c>
       <c r="B10" s="3">
-        <f t="shared" si="0"/>
-        <v>31.75</v>
+        <v>18.48</v>
       </c>
       <c r="C10" s="8">
-        <f t="shared" si="1"/>
-        <v>3.1750000000000003</v>
+        <v>3.32</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E10" s="8">
-        <v>25</v>
+        <f t="shared" si="0"/>
+        <v>14.551181102362206</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A11" s="2">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3">
+        <v>18.48</v>
+      </c>
+      <c r="C11" s="8">
+        <v>3.32</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E11" s="8">
+        <f t="shared" si="0"/>
+        <v>14.551181102362206</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A12" s="2">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3">
+        <v>18.48</v>
+      </c>
+      <c r="C12" s="8">
+        <v>3.32</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E12" s="8">
+        <f t="shared" si="0"/>
+        <v>14.551181102362206</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A13" s="2">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3">
+        <v>18.48</v>
+      </c>
+      <c r="C13" s="8">
+        <v>3.32</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E13" s="8">
+        <f t="shared" si="0"/>
+        <v>14.551181102362206</v>
       </c>
     </row>
   </sheetData>
@@ -1499,7 +1642,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1558,423 +1701,470 @@
       <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="9">
+      <c r="B2" s="28">
         <f>1.12*K2</f>
-        <v>470.40000000000003</v>
+        <v>358.40000000000003</v>
       </c>
       <c r="C2" s="8">
         <f>B2*5%</f>
-        <v>23.520000000000003</v>
+        <v>17.920000000000002</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E2" s="10">
+      <c r="E2" s="19">
         <f>1.12*L2</f>
-        <v>470.40000000000003</v>
+        <v>358.40000000000003</v>
       </c>
       <c r="F2" s="8">
         <f>E2*5%</f>
-        <v>23.520000000000003</v>
+        <v>17.920000000000002</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="H2" s="11">
+      <c r="H2" s="21">
         <f>1.12*M2</f>
-        <v>313.60000000000002</v>
+        <v>268.8</v>
       </c>
       <c r="I2" s="8">
         <f>H2*5%</f>
-        <v>15.680000000000001</v>
+        <v>13.440000000000001</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="K2" s="12">
-        <v>420</v>
-      </c>
-      <c r="L2" s="13">
-        <v>420</v>
-      </c>
-      <c r="M2" s="14">
-        <v>280</v>
+      <c r="K2" s="9">
+        <v>320</v>
+      </c>
+      <c r="L2" s="10">
+        <v>320</v>
+      </c>
+      <c r="M2" s="11">
+        <v>240</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" s="9">
-        <f t="shared" ref="B3:B10" si="0">1.12*K3</f>
-        <v>470.40000000000003</v>
+      <c r="B3" s="28">
+        <f t="shared" ref="B3:B11" si="0">1.12*K3</f>
+        <v>358.40000000000003</v>
       </c>
       <c r="C3" s="8">
-        <f t="shared" ref="C3:C10" si="1">B3*5%</f>
-        <v>23.520000000000003</v>
+        <f t="shared" ref="C3:C11" si="1">B3*5%</f>
+        <v>17.920000000000002</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="10">
-        <f t="shared" ref="E3:E10" si="2">1.12*L3</f>
-        <v>470.40000000000003</v>
+      <c r="E3" s="19">
+        <f t="shared" ref="E3:E11" si="2">1.12*L3</f>
+        <v>358.40000000000003</v>
       </c>
       <c r="F3" s="8">
-        <f t="shared" ref="F3:F10" si="3">E3*5%</f>
-        <v>23.520000000000003</v>
+        <f t="shared" ref="F3:F11" si="3">E3*5%</f>
+        <v>17.920000000000002</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="H3" s="11">
-        <f t="shared" ref="H3:H10" si="4">1.12*M3</f>
-        <v>313.60000000000002</v>
+      <c r="H3" s="21">
+        <f t="shared" ref="H3:H11" si="4">1.12*M3</f>
+        <v>268.8</v>
       </c>
       <c r="I3" s="8">
-        <f t="shared" ref="I3:I10" si="5">H3*5%</f>
-        <v>15.680000000000001</v>
+        <f t="shared" ref="I3:I11" si="5">H3*5%</f>
+        <v>13.440000000000001</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="K3" s="12">
-        <v>420</v>
-      </c>
-      <c r="L3" s="13">
-        <v>420</v>
-      </c>
-      <c r="M3" s="14">
-        <v>280</v>
+      <c r="K3" s="9">
+        <v>320</v>
+      </c>
+      <c r="L3" s="10">
+        <v>320</v>
+      </c>
+      <c r="M3" s="11">
+        <v>240</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4" s="9">
+      <c r="B4" s="28">
         <f t="shared" si="0"/>
-        <v>470.40000000000003</v>
+        <v>358.40000000000003</v>
       </c>
       <c r="C4" s="8">
         <f t="shared" si="1"/>
-        <v>23.520000000000003</v>
+        <v>17.920000000000002</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="10">
+      <c r="E4" s="19">
         <f t="shared" si="2"/>
-        <v>470.40000000000003</v>
+        <v>358.40000000000003</v>
       </c>
       <c r="F4" s="8">
         <f t="shared" si="3"/>
-        <v>23.520000000000003</v>
+        <v>17.920000000000002</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="H4" s="11">
+      <c r="H4" s="21">
         <f t="shared" si="4"/>
-        <v>313.60000000000002</v>
+        <v>268.8</v>
       </c>
       <c r="I4" s="8">
         <f t="shared" si="5"/>
-        <v>15.680000000000001</v>
+        <v>13.440000000000001</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="K4" s="12">
-        <v>420</v>
-      </c>
-      <c r="L4" s="13">
-        <v>420</v>
-      </c>
-      <c r="M4" s="14">
-        <v>280</v>
+      <c r="K4" s="9">
+        <v>320</v>
+      </c>
+      <c r="L4" s="10">
+        <v>320</v>
+      </c>
+      <c r="M4" s="11">
+        <v>240</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A5" s="2">
         <v>4</v>
       </c>
-      <c r="B5" s="9">
+      <c r="B5" s="28">
         <f t="shared" si="0"/>
-        <v>470.40000000000003</v>
+        <v>358.40000000000003</v>
       </c>
       <c r="C5" s="8">
         <f t="shared" si="1"/>
-        <v>23.520000000000003</v>
+        <v>17.920000000000002</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="10">
+      <c r="E5" s="19">
         <f t="shared" si="2"/>
-        <v>470.40000000000003</v>
+        <v>358.40000000000003</v>
       </c>
       <c r="F5" s="8">
         <f t="shared" si="3"/>
-        <v>23.520000000000003</v>
+        <v>17.920000000000002</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="H5" s="11">
+      <c r="H5" s="21">
         <f t="shared" si="4"/>
-        <v>313.60000000000002</v>
+        <v>268.8</v>
       </c>
       <c r="I5" s="8">
         <f t="shared" si="5"/>
-        <v>15.680000000000001</v>
+        <v>13.440000000000001</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="K5" s="12">
-        <v>420</v>
-      </c>
-      <c r="L5" s="13">
-        <v>420</v>
-      </c>
-      <c r="M5" s="14">
-        <v>280</v>
+      <c r="K5" s="9">
+        <v>320</v>
+      </c>
+      <c r="L5" s="10">
+        <v>320</v>
+      </c>
+      <c r="M5" s="11">
+        <v>240</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A6" s="2">
         <v>5</v>
       </c>
-      <c r="B6" s="9">
+      <c r="B6" s="28">
         <f t="shared" si="0"/>
-        <v>470.40000000000003</v>
+        <v>358.40000000000003</v>
       </c>
       <c r="C6" s="8">
         <f t="shared" si="1"/>
-        <v>23.520000000000003</v>
+        <v>17.920000000000002</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="10">
+      <c r="E6" s="19">
         <f t="shared" si="2"/>
-        <v>470.40000000000003</v>
+        <v>358.40000000000003</v>
       </c>
       <c r="F6" s="8">
-        <f t="shared" si="3"/>
-        <v>23.520000000000003</v>
+        <f>E6*5%</f>
+        <v>17.920000000000002</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="H6" s="11">
+      <c r="H6" s="21">
         <f t="shared" si="4"/>
-        <v>313.60000000000002</v>
+        <v>268.8</v>
       </c>
       <c r="I6" s="8">
         <f t="shared" si="5"/>
-        <v>15.680000000000001</v>
+        <v>13.440000000000001</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="K6" s="12">
-        <v>420</v>
-      </c>
-      <c r="L6" s="13">
-        <v>420</v>
-      </c>
-      <c r="M6" s="14">
-        <v>280</v>
+      <c r="K6" s="9">
+        <v>320</v>
+      </c>
+      <c r="L6" s="10">
+        <v>320</v>
+      </c>
+      <c r="M6" s="11">
+        <v>240</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A7" s="2">
         <v>6</v>
       </c>
-      <c r="B7" s="9">
+      <c r="B7" s="28">
         <f t="shared" si="0"/>
-        <v>470.40000000000003</v>
+        <v>358.40000000000003</v>
       </c>
       <c r="C7" s="8">
         <f t="shared" si="1"/>
-        <v>23.520000000000003</v>
+        <v>17.920000000000002</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E7" s="10">
+      <c r="E7" s="19">
         <f t="shared" si="2"/>
-        <v>470.40000000000003</v>
+        <v>358.40000000000003</v>
       </c>
       <c r="F7" s="8">
         <f t="shared" si="3"/>
-        <v>23.520000000000003</v>
+        <v>17.920000000000002</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="H7" s="11">
+      <c r="H7" s="21">
         <f t="shared" si="4"/>
-        <v>313.60000000000002</v>
+        <v>268.8</v>
       </c>
       <c r="I7" s="8">
         <f t="shared" si="5"/>
-        <v>15.680000000000001</v>
+        <v>13.440000000000001</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="K7" s="12">
-        <v>420</v>
-      </c>
-      <c r="L7" s="13">
-        <v>420</v>
-      </c>
-      <c r="M7" s="14">
-        <v>280</v>
+      <c r="K7" s="9">
+        <v>320</v>
+      </c>
+      <c r="L7" s="10">
+        <v>320</v>
+      </c>
+      <c r="M7" s="11">
+        <v>240</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A8" s="2">
         <v>7</v>
       </c>
-      <c r="B8" s="9">
+      <c r="B8" s="28">
         <f t="shared" si="0"/>
-        <v>470.40000000000003</v>
+        <v>358.40000000000003</v>
       </c>
       <c r="C8" s="8">
         <f t="shared" si="1"/>
-        <v>23.520000000000003</v>
+        <v>17.920000000000002</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E8" s="10">
+      <c r="E8" s="19">
         <f t="shared" si="2"/>
-        <v>470.40000000000003</v>
+        <v>358.40000000000003</v>
       </c>
       <c r="F8" s="8">
         <f t="shared" si="3"/>
-        <v>23.520000000000003</v>
+        <v>17.920000000000002</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="H8" s="11">
+      <c r="H8" s="21">
         <f t="shared" si="4"/>
-        <v>313.60000000000002</v>
+        <v>268.8</v>
       </c>
       <c r="I8" s="8">
         <f t="shared" si="5"/>
-        <v>15.680000000000001</v>
+        <v>13.440000000000001</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="K8" s="12">
-        <v>420</v>
-      </c>
-      <c r="L8" s="13">
-        <v>420</v>
-      </c>
-      <c r="M8" s="14">
-        <v>280</v>
+      <c r="K8" s="9">
+        <v>320</v>
+      </c>
+      <c r="L8" s="10">
+        <v>320</v>
+      </c>
+      <c r="M8" s="11">
+        <v>240</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A9" s="2">
         <v>8</v>
       </c>
-      <c r="B9" s="9">
+      <c r="B9" s="28">
         <f t="shared" si="0"/>
-        <v>470.40000000000003</v>
+        <v>358.40000000000003</v>
       </c>
       <c r="C9" s="8">
         <f t="shared" si="1"/>
-        <v>23.520000000000003</v>
+        <v>17.920000000000002</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E9" s="10">
+      <c r="E9" s="19">
         <f t="shared" si="2"/>
-        <v>470.40000000000003</v>
+        <v>358.40000000000003</v>
       </c>
       <c r="F9" s="8">
         <f t="shared" si="3"/>
-        <v>23.520000000000003</v>
+        <v>17.920000000000002</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="H9" s="11">
+      <c r="H9" s="21">
         <f t="shared" si="4"/>
-        <v>313.60000000000002</v>
+        <v>268.8</v>
       </c>
       <c r="I9" s="8">
         <f t="shared" si="5"/>
-        <v>15.680000000000001</v>
+        <v>13.440000000000001</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="K9" s="12">
-        <v>420</v>
-      </c>
-      <c r="L9" s="13">
-        <v>420</v>
-      </c>
-      <c r="M9" s="14">
-        <v>280</v>
+      <c r="K9" s="9">
+        <v>320</v>
+      </c>
+      <c r="L9" s="10">
+        <v>320</v>
+      </c>
+      <c r="M9" s="11">
+        <v>240</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A10" s="2">
         <v>9</v>
       </c>
-      <c r="B10" s="9">
+      <c r="B10" s="28">
         <f t="shared" si="0"/>
-        <v>470.40000000000003</v>
+        <v>358.40000000000003</v>
       </c>
       <c r="C10" s="8">
         <f t="shared" si="1"/>
-        <v>23.520000000000003</v>
+        <v>17.920000000000002</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E10" s="10">
+      <c r="E10" s="19">
         <f t="shared" si="2"/>
-        <v>470.40000000000003</v>
+        <v>358.40000000000003</v>
       </c>
       <c r="F10" s="8">
         <f t="shared" si="3"/>
-        <v>23.520000000000003</v>
+        <v>17.920000000000002</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="H10" s="11">
+      <c r="H10" s="21">
         <f t="shared" si="4"/>
-        <v>313.60000000000002</v>
+        <v>268.8</v>
       </c>
       <c r="I10" s="8">
         <f t="shared" si="5"/>
-        <v>15.680000000000001</v>
+        <v>13.440000000000001</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="K10" s="12">
-        <v>420</v>
-      </c>
-      <c r="L10" s="13">
-        <v>420</v>
-      </c>
-      <c r="M10" s="14">
-        <v>280</v>
+      <c r="K10" s="9">
+        <v>320</v>
+      </c>
+      <c r="L10" s="10">
+        <v>320</v>
+      </c>
+      <c r="M10" s="11">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A11" s="2">
+        <v>10</v>
+      </c>
+      <c r="B11" s="28">
+        <f t="shared" si="0"/>
+        <v>358.40000000000003</v>
+      </c>
+      <c r="C11" s="8">
+        <f t="shared" si="1"/>
+        <v>17.920000000000002</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" s="19">
+        <f t="shared" si="2"/>
+        <v>358.40000000000003</v>
+      </c>
+      <c r="F11" s="8">
+        <f t="shared" si="3"/>
+        <v>17.920000000000002</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H11" s="21">
+        <f t="shared" si="4"/>
+        <v>268.8</v>
+      </c>
+      <c r="I11" s="8">
+        <f t="shared" si="5"/>
+        <v>13.440000000000001</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K11" s="9">
+        <v>320</v>
+      </c>
+      <c r="L11" s="10">
+        <v>320</v>
+      </c>
+      <c r="M11" s="11">
+        <v>240</v>
       </c>
     </row>
   </sheetData>
@@ -1984,7 +2174,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4AF9C1D7-75F2-4ECD-8165-439BBECB938B}">
-  <dimension ref="A1:O10"/>
+  <dimension ref="A1:O11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="10.1328125" bestFit="1" customWidth="1"/>
@@ -2055,468 +2245,520 @@
       <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="15">
+      <c r="B2" s="2">
         <v>40</v>
       </c>
-      <c r="C2" s="16">
+      <c r="C2" s="2">
         <v>40</v>
       </c>
-      <c r="D2" s="15">
+      <c r="D2" s="2">
         <f>Geometri!F2-Tulangan!B2-Tulangan!M2-0.5*Tulangan!G2</f>
         <v>242</v>
       </c>
-      <c r="E2" s="16">
+      <c r="E2" s="2">
         <f>C2+M2+0.5*I2</f>
         <v>58</v>
       </c>
-      <c r="F2" s="15">
-        <v>4</v>
-      </c>
-      <c r="G2" s="10">
+      <c r="F2" s="2">
+        <v>3</v>
+      </c>
+      <c r="G2" s="3">
         <v>16</v>
       </c>
-      <c r="H2" s="15">
-        <v>4</v>
-      </c>
-      <c r="I2" s="10">
+      <c r="H2" s="2">
+        <v>3</v>
+      </c>
+      <c r="I2" s="3">
         <v>16</v>
       </c>
-      <c r="J2" s="17">
-        <f>F2*(1/4)*PI()*G2^2</f>
-        <v>804.24771931898704</v>
-      </c>
-      <c r="K2" s="18">
+      <c r="J2" s="22">
+        <f t="shared" ref="J2:J6" si="0">F2*(1/4)*PI()*G2^2</f>
+        <v>603.18578948924028</v>
+      </c>
+      <c r="K2" s="22">
         <f>H2*(1/4)*PI()*I2^2</f>
-        <v>804.24771931898704</v>
-      </c>
-      <c r="L2" s="19">
+        <v>603.18578948924028</v>
+      </c>
+      <c r="L2" s="3">
         <v>2</v>
       </c>
-      <c r="M2" s="20">
+      <c r="M2" s="3">
         <v>10</v>
       </c>
-      <c r="N2" s="21">
+      <c r="N2" s="22">
         <f>L2*(1/4)*PI()*M2^2</f>
         <v>157.07963267948966</v>
       </c>
-      <c r="O2" s="20">
-        <v>150</v>
+      <c r="O2" s="3">
+        <v>200</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="13.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" s="15">
+      <c r="B3" s="2">
         <v>40</v>
       </c>
-      <c r="C3" s="16">
+      <c r="C3" s="2">
         <v>40</v>
       </c>
-      <c r="D3" s="15">
+      <c r="D3" s="2">
         <f>Geometri!F3-Tulangan!B3-Tulangan!M3-0.5*Tulangan!G3</f>
         <v>242</v>
       </c>
-      <c r="E3" s="16">
-        <f t="shared" ref="E3:E10" si="0">C3+M3+0.5*I3</f>
+      <c r="E3" s="2">
+        <f t="shared" ref="E3:E11" si="1">C3+M3+0.5*I3</f>
         <v>58</v>
       </c>
-      <c r="F3" s="15">
-        <v>4</v>
-      </c>
-      <c r="G3" s="10">
+      <c r="F3" s="2">
+        <v>3</v>
+      </c>
+      <c r="G3" s="3">
         <v>16</v>
       </c>
-      <c r="H3" s="15">
-        <v>4</v>
-      </c>
-      <c r="I3" s="10">
+      <c r="H3" s="2">
+        <v>3</v>
+      </c>
+      <c r="I3" s="3">
         <v>16</v>
       </c>
-      <c r="J3" s="17">
-        <f t="shared" ref="J3:J10" si="1">F3*(1/4)*PI()*G3^2</f>
-        <v>804.24771931898704</v>
-      </c>
-      <c r="K3" s="18">
-        <f t="shared" ref="K3:K10" si="2">H3*(1/4)*PI()*I3^2</f>
-        <v>804.24771931898704</v>
-      </c>
-      <c r="L3" s="19">
+      <c r="J3" s="22">
+        <f t="shared" si="0"/>
+        <v>603.18578948924028</v>
+      </c>
+      <c r="K3" s="22">
+        <f t="shared" ref="K3:K6" si="2">H3*(1/4)*PI()*I3^2</f>
+        <v>603.18578948924028</v>
+      </c>
+      <c r="L3" s="3">
         <v>2</v>
       </c>
-      <c r="M3" s="20">
+      <c r="M3" s="3">
         <v>10</v>
       </c>
-      <c r="N3" s="21">
-        <f t="shared" ref="N3:N10" si="3">L3*(1/4)*PI()*M3^2</f>
+      <c r="N3" s="22">
+        <f t="shared" ref="N3:N11" si="3">L3*(1/4)*PI()*M3^2</f>
         <v>157.07963267948966</v>
       </c>
-      <c r="O3" s="20">
-        <v>150</v>
+      <c r="O3" s="3">
+        <v>200</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="13.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4" s="15">
+      <c r="B4" s="2">
         <v>40</v>
       </c>
-      <c r="C4" s="16">
+      <c r="C4" s="2">
         <v>40</v>
       </c>
-      <c r="D4" s="15">
+      <c r="D4" s="2">
         <f>Geometri!F4-Tulangan!B4-Tulangan!M4-0.5*Tulangan!G4</f>
         <v>242</v>
       </c>
-      <c r="E4" s="16">
+      <c r="E4" s="2">
+        <f t="shared" si="1"/>
+        <v>58</v>
+      </c>
+      <c r="F4" s="2">
+        <v>3</v>
+      </c>
+      <c r="G4" s="3">
+        <v>16</v>
+      </c>
+      <c r="H4" s="2">
+        <v>3</v>
+      </c>
+      <c r="I4" s="3">
+        <v>16</v>
+      </c>
+      <c r="J4" s="22">
         <f t="shared" si="0"/>
-        <v>58</v>
-      </c>
-      <c r="F4" s="15">
-        <v>4</v>
-      </c>
-      <c r="G4" s="10">
-        <v>16</v>
-      </c>
-      <c r="H4" s="15">
-        <v>4</v>
-      </c>
-      <c r="I4" s="10">
-        <v>16</v>
-      </c>
-      <c r="J4" s="17">
-        <f t="shared" si="1"/>
-        <v>804.24771931898704</v>
-      </c>
-      <c r="K4" s="18">
+        <v>603.18578948924028</v>
+      </c>
+      <c r="K4" s="22">
         <f t="shared" si="2"/>
-        <v>804.24771931898704</v>
-      </c>
-      <c r="L4" s="19">
+        <v>603.18578948924028</v>
+      </c>
+      <c r="L4" s="3">
         <v>2</v>
       </c>
-      <c r="M4" s="20">
+      <c r="M4" s="3">
         <v>10</v>
       </c>
-      <c r="N4" s="21">
+      <c r="N4" s="22">
         <f t="shared" si="3"/>
         <v>157.07963267948966</v>
       </c>
-      <c r="O4" s="20">
-        <v>150</v>
+      <c r="O4" s="3">
+        <v>200</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="13.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="2">
         <v>4</v>
       </c>
-      <c r="B5" s="15">
+      <c r="B5" s="2">
         <v>40</v>
       </c>
-      <c r="C5" s="16">
+      <c r="C5" s="2">
         <v>40</v>
       </c>
-      <c r="D5" s="15">
+      <c r="D5" s="2">
         <f>Geometri!F5-Tulangan!B5-Tulangan!M5-0.5*Tulangan!G5</f>
         <v>242</v>
       </c>
-      <c r="E5" s="16">
+      <c r="E5" s="2">
+        <f t="shared" si="1"/>
+        <v>58</v>
+      </c>
+      <c r="F5" s="2">
+        <v>3</v>
+      </c>
+      <c r="G5" s="3">
+        <v>16</v>
+      </c>
+      <c r="H5" s="2">
+        <v>3</v>
+      </c>
+      <c r="I5" s="3">
+        <v>16</v>
+      </c>
+      <c r="J5" s="22">
         <f t="shared" si="0"/>
-        <v>58</v>
-      </c>
-      <c r="F5" s="15">
-        <v>4</v>
-      </c>
-      <c r="G5" s="10">
-        <v>16</v>
-      </c>
-      <c r="H5" s="15">
-        <v>4</v>
-      </c>
-      <c r="I5" s="10">
-        <v>16</v>
-      </c>
-      <c r="J5" s="17">
-        <f t="shared" si="1"/>
-        <v>804.24771931898704</v>
-      </c>
-      <c r="K5" s="18">
+        <v>603.18578948924028</v>
+      </c>
+      <c r="K5" s="22">
         <f t="shared" si="2"/>
-        <v>804.24771931898704</v>
-      </c>
-      <c r="L5" s="19">
+        <v>603.18578948924028</v>
+      </c>
+      <c r="L5" s="3">
         <v>2</v>
       </c>
-      <c r="M5" s="20">
+      <c r="M5" s="3">
         <v>10</v>
       </c>
-      <c r="N5" s="21">
+      <c r="N5" s="22">
         <f t="shared" si="3"/>
         <v>157.07963267948966</v>
       </c>
-      <c r="O5" s="20">
-        <v>150</v>
+      <c r="O5" s="3">
+        <v>200</v>
       </c>
     </row>
     <row r="6" spans="1:15" ht="13.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="2">
         <v>5</v>
       </c>
-      <c r="B6" s="15">
+      <c r="B6" s="2">
         <v>40</v>
       </c>
-      <c r="C6" s="16">
+      <c r="C6" s="2">
         <v>40</v>
       </c>
-      <c r="D6" s="15">
+      <c r="D6" s="2">
         <f>Geometri!F6-Tulangan!B6-Tulangan!M6-0.5*Tulangan!G6</f>
         <v>242</v>
       </c>
-      <c r="E6" s="16">
+      <c r="E6" s="2">
+        <f t="shared" si="1"/>
+        <v>58</v>
+      </c>
+      <c r="F6" s="2">
+        <v>3</v>
+      </c>
+      <c r="G6" s="3">
+        <v>16</v>
+      </c>
+      <c r="H6" s="2">
+        <v>3</v>
+      </c>
+      <c r="I6" s="3">
+        <v>16</v>
+      </c>
+      <c r="J6" s="22">
         <f t="shared" si="0"/>
-        <v>58</v>
-      </c>
-      <c r="F6" s="15">
-        <v>4</v>
-      </c>
-      <c r="G6" s="10">
-        <v>16</v>
-      </c>
-      <c r="H6" s="15">
-        <v>4</v>
-      </c>
-      <c r="I6" s="10">
-        <v>16</v>
-      </c>
-      <c r="J6" s="17">
-        <f t="shared" si="1"/>
-        <v>804.24771931898704</v>
-      </c>
-      <c r="K6" s="18">
+        <v>603.18578948924028</v>
+      </c>
+      <c r="K6" s="22">
         <f t="shared" si="2"/>
-        <v>804.24771931898704</v>
-      </c>
-      <c r="L6" s="19">
+        <v>603.18578948924028</v>
+      </c>
+      <c r="L6" s="3">
         <v>2</v>
       </c>
-      <c r="M6" s="20">
+      <c r="M6" s="3">
         <v>10</v>
       </c>
-      <c r="N6" s="21">
+      <c r="N6" s="22">
         <f t="shared" si="3"/>
         <v>157.07963267948966</v>
       </c>
-      <c r="O6" s="20">
-        <v>150</v>
+      <c r="O6" s="3">
+        <v>200</v>
       </c>
     </row>
     <row r="7" spans="1:15" ht="13.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="2">
         <v>6</v>
       </c>
-      <c r="B7" s="15">
+      <c r="B7" s="2">
         <v>40</v>
       </c>
-      <c r="C7" s="16">
+      <c r="C7" s="2">
         <v>40</v>
       </c>
-      <c r="D7" s="15">
+      <c r="D7" s="2">
         <f>Geometri!F7-Tulangan!B7-Tulangan!M7-0.5*Tulangan!G7</f>
         <v>242</v>
       </c>
-      <c r="E7" s="16">
-        <f t="shared" si="0"/>
+      <c r="E7" s="2">
+        <f t="shared" si="1"/>
         <v>58</v>
       </c>
-      <c r="F7" s="15">
-        <v>4</v>
-      </c>
-      <c r="G7" s="10">
+      <c r="F7" s="2">
+        <v>3</v>
+      </c>
+      <c r="G7" s="3">
         <v>16</v>
       </c>
-      <c r="H7" s="15">
-        <v>4</v>
-      </c>
-      <c r="I7" s="10">
+      <c r="H7" s="2">
+        <v>3</v>
+      </c>
+      <c r="I7" s="3">
         <v>16</v>
       </c>
-      <c r="J7" s="17">
-        <f t="shared" si="1"/>
-        <v>804.24771931898704</v>
-      </c>
-      <c r="K7" s="18">
-        <f t="shared" si="2"/>
-        <v>804.24771931898704</v>
-      </c>
-      <c r="L7" s="19">
+      <c r="J7" s="22">
+        <f>F7*(1/4)*PI()*G7^2</f>
+        <v>603.18578948924028</v>
+      </c>
+      <c r="K7" s="22">
+        <f>H7*(1/4)*PI()*I7^2</f>
+        <v>603.18578948924028</v>
+      </c>
+      <c r="L7" s="3">
         <v>2</v>
       </c>
-      <c r="M7" s="20">
+      <c r="M7" s="3">
         <v>10</v>
       </c>
-      <c r="N7" s="21">
+      <c r="N7" s="22">
         <f t="shared" si="3"/>
         <v>157.07963267948966</v>
       </c>
-      <c r="O7" s="20">
-        <v>150</v>
+      <c r="O7" s="3">
+        <v>200</v>
       </c>
     </row>
     <row r="8" spans="1:15" ht="13.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="2">
         <v>7</v>
       </c>
-      <c r="B8" s="15">
+      <c r="B8" s="12">
         <v>40</v>
       </c>
-      <c r="C8" s="16">
+      <c r="C8" s="13">
         <v>40</v>
       </c>
-      <c r="D8" s="15">
+      <c r="D8" s="12">
         <f>Geometri!F8-Tulangan!B8-Tulangan!M8-0.5*Tulangan!G8</f>
         <v>442</v>
       </c>
-      <c r="E8" s="16">
-        <f t="shared" si="0"/>
+      <c r="E8" s="13">
+        <f t="shared" si="1"/>
         <v>58</v>
       </c>
-      <c r="F8" s="15">
-        <v>4</v>
-      </c>
-      <c r="G8" s="10">
+      <c r="F8" s="12">
+        <v>6</v>
+      </c>
+      <c r="G8" s="3">
         <v>16</v>
       </c>
-      <c r="H8" s="15">
+      <c r="H8" s="12">
+        <v>3</v>
+      </c>
+      <c r="I8" s="3">
+        <v>16</v>
+      </c>
+      <c r="J8" s="14">
+        <f>F8*(1/4)*PI()*G8^2</f>
+        <v>1206.3715789784806</v>
+      </c>
+      <c r="K8" s="15">
+        <f>H8*(1/4)*PI()*I8^2</f>
+        <v>603.18578948924028</v>
+      </c>
+      <c r="L8" s="16">
         <v>2</v>
       </c>
-      <c r="I8" s="10">
-        <v>16</v>
-      </c>
-      <c r="J8" s="17">
-        <f t="shared" si="1"/>
-        <v>804.24771931898704</v>
-      </c>
-      <c r="K8" s="18">
-        <f t="shared" si="2"/>
-        <v>402.12385965949352</v>
-      </c>
-      <c r="L8" s="19">
-        <v>2</v>
-      </c>
-      <c r="M8" s="20">
+      <c r="M8" s="17">
         <v>10</v>
       </c>
-      <c r="N8" s="21">
+      <c r="N8" s="18">
         <f t="shared" si="3"/>
         <v>157.07963267948966</v>
       </c>
-      <c r="O8" s="20">
-        <v>150</v>
+      <c r="O8" s="3">
+        <v>200</v>
       </c>
     </row>
     <row r="9" spans="1:15" ht="13.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="2">
         <v>8</v>
       </c>
-      <c r="B9" s="15">
+      <c r="B9" s="12">
         <v>40</v>
       </c>
-      <c r="C9" s="16">
+      <c r="C9" s="13">
         <v>40</v>
       </c>
-      <c r="D9" s="15">
+      <c r="D9" s="12">
         <f>Geometri!F9-Tulangan!B9-Tulangan!M9-0.5*Tulangan!G9</f>
         <v>442</v>
       </c>
-      <c r="E9" s="16">
-        <f t="shared" si="0"/>
+      <c r="E9" s="13">
+        <f t="shared" si="1"/>
         <v>58</v>
       </c>
-      <c r="F9" s="15">
-        <v>4</v>
-      </c>
-      <c r="G9" s="10">
+      <c r="F9" s="12">
+        <v>6</v>
+      </c>
+      <c r="G9" s="3">
         <v>16</v>
       </c>
-      <c r="H9" s="15">
+      <c r="H9" s="12">
+        <v>3</v>
+      </c>
+      <c r="I9" s="3">
+        <v>16</v>
+      </c>
+      <c r="J9" s="14">
+        <f t="shared" ref="J9" si="4">F9*(1/4)*PI()*G9^2</f>
+        <v>1206.3715789784806</v>
+      </c>
+      <c r="K9" s="15">
+        <f>H9*(1/4)*PI()*I9^2</f>
+        <v>603.18578948924028</v>
+      </c>
+      <c r="L9" s="16">
         <v>2</v>
       </c>
-      <c r="I9" s="10">
-        <v>16</v>
-      </c>
-      <c r="J9" s="17">
-        <f t="shared" si="1"/>
-        <v>804.24771931898704</v>
-      </c>
-      <c r="K9" s="18">
-        <f t="shared" si="2"/>
-        <v>402.12385965949352</v>
-      </c>
-      <c r="L9" s="19">
-        <v>2</v>
-      </c>
-      <c r="M9" s="20">
+      <c r="M9" s="17">
         <v>10</v>
       </c>
-      <c r="N9" s="21">
+      <c r="N9" s="18">
         <f t="shared" si="3"/>
         <v>157.07963267948966</v>
       </c>
-      <c r="O9" s="20">
-        <v>150</v>
+      <c r="O9" s="3">
+        <v>200</v>
       </c>
     </row>
     <row r="10" spans="1:15" ht="13.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="2">
         <v>9</v>
       </c>
-      <c r="B10" s="15">
+      <c r="B10" s="12">
         <v>40</v>
       </c>
-      <c r="C10" s="16">
+      <c r="C10" s="13">
         <v>40</v>
       </c>
-      <c r="D10" s="15">
+      <c r="D10" s="12">
         <f>Geometri!F10-Tulangan!B10-Tulangan!M10-0.5*Tulangan!G10</f>
-        <v>242</v>
-      </c>
-      <c r="E10" s="16">
-        <f t="shared" si="0"/>
+        <v>292</v>
+      </c>
+      <c r="E10" s="13">
+        <f t="shared" si="1"/>
         <v>58</v>
       </c>
-      <c r="F10" s="15">
+      <c r="F10" s="12">
         <v>4</v>
       </c>
-      <c r="G10" s="10">
+      <c r="G10" s="3">
         <v>16</v>
       </c>
-      <c r="H10" s="15">
+      <c r="H10" s="12">
         <v>2</v>
       </c>
-      <c r="I10" s="10">
+      <c r="I10" s="3">
         <v>16</v>
       </c>
-      <c r="J10" s="17">
-        <f t="shared" si="1"/>
+      <c r="J10" s="14">
+        <f>F10*(1/4)*PI()*G10^2</f>
         <v>804.24771931898704</v>
       </c>
-      <c r="K10" s="18">
-        <f t="shared" si="2"/>
+      <c r="K10" s="15">
+        <f>H10*(1/4)*PI()*I10^2</f>
         <v>402.12385965949352</v>
       </c>
-      <c r="L10" s="19">
+      <c r="L10" s="16">
         <v>2</v>
       </c>
-      <c r="M10" s="20">
+      <c r="M10" s="17">
         <v>10</v>
       </c>
-      <c r="N10" s="21">
+      <c r="N10" s="18">
         <f t="shared" si="3"/>
         <v>157.07963267948966</v>
       </c>
-      <c r="O10" s="20">
-        <v>150</v>
+      <c r="O10" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" ht="13.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A11" s="2">
+        <v>10</v>
+      </c>
+      <c r="B11" s="12">
+        <v>40</v>
+      </c>
+      <c r="C11" s="13">
+        <v>40</v>
+      </c>
+      <c r="D11" s="12">
+        <f>Geometri!F11-Tulangan!B11-Tulangan!M11-0.5*Tulangan!G11</f>
+        <v>292</v>
+      </c>
+      <c r="E11" s="13">
+        <f t="shared" si="1"/>
+        <v>58</v>
+      </c>
+      <c r="F11" s="12">
+        <v>4</v>
+      </c>
+      <c r="G11" s="3">
+        <v>16</v>
+      </c>
+      <c r="H11" s="12">
+        <v>2</v>
+      </c>
+      <c r="I11" s="3">
+        <v>16</v>
+      </c>
+      <c r="J11" s="14">
+        <f>F11*(1/4)*PI()*G11^2</f>
+        <v>804.24771931898704</v>
+      </c>
+      <c r="K11" s="15">
+        <f>H11*(1/4)*PI()*I11^2</f>
+        <v>402.12385965949352</v>
+      </c>
+      <c r="L11" s="16">
+        <v>2</v>
+      </c>
+      <c r="M11" s="17">
+        <v>10</v>
+      </c>
+      <c r="N11" s="18">
+        <f t="shared" si="3"/>
+        <v>157.07963267948966</v>
+      </c>
+      <c r="O11" s="3">
+        <v>200</v>
       </c>
     </row>
   </sheetData>
@@ -2526,7 +2768,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="4" width="15" customWidth="1"/>
@@ -2555,18 +2797,18 @@
         <v>7</v>
       </c>
       <c r="B2" s="8">
-        <f>1.05*E2</f>
-        <v>105</v>
+        <v>35.200000000000003</v>
       </c>
       <c r="C2" s="8">
         <f>20%*B2</f>
-        <v>21</v>
+        <v>7.0400000000000009</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E2" s="8">
-        <v>100</v>
+        <f>B2</f>
+        <v>35.200000000000003</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.45">
@@ -2574,18 +2816,18 @@
         <v>8</v>
       </c>
       <c r="B3" s="8">
-        <f t="shared" ref="B3:B4" si="0">1.05*E3</f>
-        <v>105</v>
+        <v>35.200000000000003</v>
       </c>
       <c r="C3" s="8">
-        <f t="shared" ref="C3:C4" si="1">20%*B3</f>
-        <v>21</v>
+        <f t="shared" ref="C3" si="0">20%*B3</f>
+        <v>7.0400000000000009</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E3" s="8">
-        <v>100</v>
+        <f t="shared" ref="E3" si="1">B3</f>
+        <v>35.200000000000003</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.45">
@@ -2593,18 +2835,37 @@
         <v>9</v>
       </c>
       <c r="B4" s="8">
-        <f t="shared" si="0"/>
-        <v>105</v>
+        <v>7.38</v>
       </c>
       <c r="C4" s="8">
-        <f t="shared" si="1"/>
-        <v>21</v>
+        <f>20%*B4</f>
+        <v>1.476</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E4" s="8">
-        <v>100</v>
+        <f>B4</f>
+        <v>7.38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A5" s="3">
+        <v>10</v>
+      </c>
+      <c r="B5" s="8">
+        <v>7.38</v>
+      </c>
+      <c r="C5" s="8">
+        <f>20%*B5</f>
+        <v>1.476</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="8">
+        <f>B5</f>
+        <v>7.38</v>
       </c>
     </row>
   </sheetData>
@@ -2614,7 +2875,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="4" width="15" customWidth="1"/>
@@ -2643,18 +2904,18 @@
         <v>7</v>
       </c>
       <c r="B2" s="8">
-        <f>1*E2</f>
-        <v>40</v>
+        <v>28.74</v>
       </c>
       <c r="C2" s="8">
         <f>20%*B2</f>
-        <v>8</v>
+        <v>5.7480000000000002</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E2" s="8">
-        <v>40</v>
+        <f>B2</f>
+        <v>28.74</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.45">
@@ -2662,18 +2923,18 @@
         <v>8</v>
       </c>
       <c r="B3" s="8">
-        <f t="shared" ref="B3:B4" si="0">1*E3</f>
-        <v>40</v>
+        <v>28.74</v>
       </c>
       <c r="C3" s="8">
-        <f t="shared" ref="C3:C4" si="1">20%*B3</f>
-        <v>8</v>
+        <f>20%*B3</f>
+        <v>5.7480000000000002</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E3" s="8">
-        <v>40</v>
+        <f t="shared" ref="E3:E5" si="0">B3</f>
+        <v>28.74</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.45">
@@ -2681,18 +2942,37 @@
         <v>9</v>
       </c>
       <c r="B4" s="8">
-        <f t="shared" si="0"/>
-        <v>40</v>
+        <v>8.16</v>
       </c>
       <c r="C4" s="8">
-        <f t="shared" si="1"/>
-        <v>8</v>
+        <f>20%*B4</f>
+        <v>1.6320000000000001</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E4" s="8">
-        <v>40</v>
+        <f t="shared" si="0"/>
+        <v>8.16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A5" s="3">
+        <v>10</v>
+      </c>
+      <c r="B5" s="8">
+        <v>8.16</v>
+      </c>
+      <c r="C5" s="8">
+        <f>20%*B5</f>
+        <v>1.6320000000000001</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="8">
+        <f t="shared" si="0"/>
+        <v>8.16</v>
       </c>
     </row>
   </sheetData>
@@ -2702,7 +2982,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="4" width="12" customWidth="1"/>
@@ -2724,43 +3004,15 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A2" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B2" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C2" s="3">
         <v>0</v>
       </c>
       <c r="D2" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A3" s="3">
-        <v>3</v>
-      </c>
-      <c r="B3" s="3">
-        <v>200</v>
-      </c>
-      <c r="C3" s="3">
-        <v>0</v>
-      </c>
-      <c r="D3" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A4" s="3">
-        <v>4</v>
-      </c>
-      <c r="B4" s="3">
-        <v>300</v>
-      </c>
-      <c r="C4" s="3">
-        <v>0</v>
-      </c>
-      <c r="D4" s="3">
         <v>0</v>
       </c>
     </row>
